--- a/output/pdf_financials_xlsx/BRY.xlsx
+++ b/output/pdf_financials_xlsx/BRY.xlsx
@@ -7679,16 +7679,16 @@
         <v>-9.928214000000001</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.090128</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-0.825</v>
+        <v>-1.530014</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.522468</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-7.041311</v>
+        <v>-7.495357</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>-0.206116</v>
@@ -7737,16 +7737,16 @@
         <v>-9.928214000000001</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.090128</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-0.825</v>
+        <v>-1.530014</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.522468</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-7.041311</v>
+        <v>-7.495357</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>-0.206116</v>
@@ -33802,7 +33802,11 @@
           <t>Principal portion of lease payments 6</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BRY.xlsx
+++ b/output/pdf_financials_xlsx/BRY.xlsx
@@ -2097,49 +2097,49 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.954973</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.986082</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.326865</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.44256</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1.013097</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1.486362</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2.16749</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>1.610928</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1.063916</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.954453</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>1.066033</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.480545</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>10.956288</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>16.469127</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>17.322954</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2155,40 +2155,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.497018</v>
+        <v>7.451991</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.770057</v>
+        <v>-8.783975</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.939885</v>
+        <v>10.26675</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>12.820072</v>
+        <v>13.262632</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.484052</v>
+        <v>7.497149</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.529465</v>
+        <v>8.015827</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.802831</v>
+        <v>3.970321</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-14.323331</v>
+        <v>-12.712403</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.542078</v>
+        <v>-4.478162</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.157</v>
+        <v>3.111453</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.139648</v>
+        <v>-6.073615</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.640607</v>
+        <v>-2.160062</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2219,40 +2219,40 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5.838293555182481</v>
+        <v>6.696443049500227</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-10.12655056718458</v>
+        <v>-9.10448803096903</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.518154588624733</v>
+        <v>6.732498778684359</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.887867923714487</v>
+        <v>7.125643095984898</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.074311554161641</v>
+        <v>4.710900035035405</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.351823317438924</v>
+        <v>5.342468769976789</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.9760452839976299</v>
+        <v>2.149515449871205</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-14.79345517055614</v>
+        <v>-13.12965286430533</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-8.925688089278172</v>
+        <v>-7.212218454027193</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1.856123878447688</v>
+        <v>2.67744191468136</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-5.879326571132123</v>
+        <v>-5.001474309703592</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-3.969001120794222</v>
+        <v>-2.354906338142241</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -6257,40 +6257,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.954973</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.986082</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.326865</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.44256</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.820097</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.486362</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.16749</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.610928</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.063916</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.954453</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.066033</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.480545</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.025025</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.074096</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.085491</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.016632</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.06472799999999999</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.025052</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -6989,19 +6989,19 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.083754</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.007146</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.011638</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="113">
@@ -31406,7 +31406,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -34299,7 +34303,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>0.025025</v>
       </c>
@@ -35400,7 +35408,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -39334,7 +39346,11 @@
           <t>Amortization on intangible assets 7</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -40237,7 +40253,11 @@
           <t>Amortization on intangible assets 8</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -42021,7 +42041,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -43120,7 +43144,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -43219,7 +43247,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E352" s="5" t="n">
         <v>0.954973</v>
       </c>
@@ -53822,7 +53854,11 @@
           <t>Depreciation on property and equipment total</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -55522,7 +55558,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -59038,7 +59078,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E513" s="5" t="n">
         <v>0.954973</v>
       </c>

--- a/output/pdf_financials_xlsx/BRY.xlsx
+++ b/output/pdf_financials_xlsx/BRY.xlsx
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.01023</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1.322719</v>
@@ -1370,10 +1370,10 @@
         <v>-1.406886</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>4.974881</v>
+        <v>1.123454</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>0.775194</v>
       </c>
     </row>
     <row r="18">
@@ -1566,16 +1566,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>4.486788</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-8.447338</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.095727</v>
+        <v>6.973587</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>9.462267000000001</v>
@@ -1620,12 +1618,10 @@
         </is>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.851427</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0.979033</v>
       </c>
     </row>
     <row r="21">
@@ -1650,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-4.666234</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-12.412413</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -1751,13 +1747,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.497018</v>
+        <v>4.486788</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-8.447338</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.095727</v>
+        <v>6.973587</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>9.462267000000001</v>
@@ -1802,10 +1798,10 @@
         </is>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0</v>
+        <v>-3.851427</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.203839</v>
+        <v>0.979033</v>
       </c>
     </row>
     <row r="24">
@@ -1967,7 +1963,7 @@
         <v>14.564376</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>13.91319</v>
+        <v>13.6737</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>15.511913</v>
@@ -2283,7 +2279,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>30.94081007625345</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-13.53849829125869</v>
@@ -2334,10 +2330,10 @@
         </is>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-100</v>
+        <v>-22.58253011479069</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>380.2971953355344</v>
       </c>
     </row>
     <row r="32">
@@ -2347,13 +2343,13 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5.838293555182481</v>
+        <v>4.031878234579326</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>-8.755567691682849</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.653076519967627</v>
+        <v>4.572982293379027</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>5.083812739501159</v>
@@ -2398,10 +2394,10 @@
         </is>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0</v>
+        <v>-4.636217027508979</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>0.269625507195461</v>
+        <v>1.295003748969009</v>
       </c>
     </row>
     <row r="33">
@@ -2775,19 +2771,19 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.7585</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.097273</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.487457</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.06579</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.050883</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -2802,19 +2798,19 @@
         <v>0.260087</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.193176</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.800112</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.291241</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.181176</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.354564</v>
       </c>
     </row>
     <row r="41">
@@ -2833,19 +2829,19 @@
         <v>31.172888</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>56.86066</v>
+        <v>57.61916</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>37.594701</v>
+        <v>37.691974</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45.877585</v>
+        <v>46.365042</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>45.465731</v>
+        <v>45.531521</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16.447331</v>
+        <v>16.498214</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>18.999389</v>
@@ -2860,19 +2856,19 @@
         <v>16.9349</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.342143</v>
+        <v>19.535319</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>30.919042</v>
+        <v>31.719154</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>24.943378</v>
+        <v>25.234619</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>17.935856</v>
+        <v>18.117032</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>9.321071</v>
+        <v>9.675635</v>
       </c>
     </row>
     <row r="42">
@@ -3239,19 +3235,19 @@
         <v>22.968359</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.981023</v>
+        <v>1.222523</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.711738</v>
+        <v>2.614465</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.032024</v>
+        <v>4.544567</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.46787</v>
+        <v>2.40208</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.061313</v>
+        <v>5.01043</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>3.365631</v>
@@ -3266,19 +3262,19 @@
         <v>0.24002</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.674048</v>
+        <v>0.480872</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.623674</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.438764</v>
+        <v>0.147523</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.462032</v>
+        <v>0.280856</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.502017</v>
+        <v>0.147453</v>
       </c>
     </row>
     <row r="49">
@@ -3963,10 +3959,10 @@
         <v>4.7283</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>0.002009</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0</v>
+        <v>0.00201</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0.548466</v>
@@ -4024,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.605483</v>
+        <v>32.603473</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>114.152908</v>
@@ -4383,46 +4379,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.731278</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>3.964305</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.815474</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.422077</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>1.395421</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>2.250995</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>2.184416</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.153046</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.803744</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.276614</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>4.311038</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.444157</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.488477</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>1.600462</v>
       </c>
     </row>
     <row r="68">
@@ -6193,7 +6189,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>6.497018</v>
+        <v>4.486788</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-8.447338</v>
@@ -6244,10 +6240,10 @@
         </is>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>0</v>
+        <v>-3.851427</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>0.203839</v>
+        <v>0.979033</v>
       </c>
     </row>
     <row r="100">
@@ -7185,25 +7181,25 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.208458</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.035338</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.02805</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.040706</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.020994</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.050589</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.014454</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -7478,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.110314</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.584928</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -7490,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.184951</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.215238</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.211196</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -35598,7 +35594,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -40152,7 +40152,11 @@
           <t>Repurchases of shares 16</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -40556,7 +40560,11 @@
           <t>Deferred tax expense/(recovery)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41152,7 +41160,11 @@
           <t>Repurchases of shares 17</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -41554,7 +41566,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E335" s="5" t="n">
         <v>-0.208458</v>
       </c>
@@ -42245,7 +42261,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -42546,7 +42566,11 @@
           <t>Repurchases of shares</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -43633,7 +43657,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -44730,7 +44758,11 @@
           <t>Repurchase common shares 17</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45944,7 +45976,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -47936,7 +47972,11 @@
           <t>Repurchase of common shares (Note 20)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -48435,7 +48475,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E404" s="5" t="n">
         <v>-0.219183</v>
       </c>
@@ -48934,7 +48978,11 @@
           <t>Change in non-cash operating working capital (Note 16)</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49132,7 +49180,11 @@
           <t>Repurchase of common shares (Note 12)</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49837,7 +49889,11 @@
           <t>Repurchase of common shares (Note 13)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -51688,7 +51744,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E437" s="5" t="n">
         <v>2.01023</v>
       </c>
@@ -54248,7 +54308,11 @@
           <t>Income tax (recovery) / expense total</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -58575,7 +58639,11 @@
           <t>Net earnings / (loss)</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -59670,7 +59738,11 @@
           <t>Income tax (recovery)/expense total</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -61058,7 +61130,11 @@
           <t>Net loss from discontinued operations 21</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -68195,7 +68271,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
           <t>-</t>
